--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.7718573937743</v>
+        <v>4.512926826488324</v>
       </c>
       <c r="D2" t="n">
-        <v>19.82839153090814</v>
+        <v>3.222113623772573</v>
       </c>
       <c r="E2" t="n">
-        <v>14.22108109476125</v>
+        <v>2.310925677898703</v>
       </c>
       <c r="F2" t="n">
-        <v>13.31060154401913</v>
+        <v>2.162972750903108</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.63312036796452</v>
+        <v>5.302882059794235</v>
       </c>
       <c r="D3" t="n">
-        <v>32.33576162960632</v>
+        <v>5.254561264811028</v>
       </c>
       <c r="E3" t="n">
-        <v>14.22108109476125</v>
+        <v>2.310925677898703</v>
       </c>
       <c r="F3" t="n">
-        <v>13.31060154401913</v>
+        <v>2.162972750903108</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.56225274157379</v>
+        <v>6.103866070505742</v>
       </c>
       <c r="D4" t="n">
-        <v>37.40673873149503</v>
+        <v>6.078595043867943</v>
       </c>
       <c r="E4" t="n">
-        <v>14.22108109476125</v>
+        <v>2.310925677898703</v>
       </c>
       <c r="F4" t="n">
-        <v>13.31060154401913</v>
+        <v>2.162972750903108</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.34872686584185</v>
+        <v>7.6941681156993</v>
       </c>
       <c r="D5" t="n">
-        <v>46.93974712862821</v>
+        <v>7.627708908402083</v>
       </c>
       <c r="E5" t="n">
-        <v>14.22108109476125</v>
+        <v>2.310925677898703</v>
       </c>
       <c r="F5" t="n">
-        <v>13.31060154401913</v>
+        <v>2.162972750903108</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>49.08212708835164</v>
+        <v>7.975845651857142</v>
       </c>
       <c r="D6" t="n">
-        <v>29.71414601452953</v>
+        <v>4.828548727361048</v>
       </c>
       <c r="E6" t="n">
-        <v>14.22108109476125</v>
+        <v>2.310925677898703</v>
       </c>
       <c r="F6" t="n">
-        <v>13.31060154401913</v>
+        <v>2.162972750903108</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.47785925649261</v>
+        <v>7.065152129180049</v>
       </c>
       <c r="D7" t="n">
-        <v>36.25394262710016</v>
+        <v>5.891265676903776</v>
       </c>
       <c r="E7" t="n">
-        <v>14.22108109476125</v>
+        <v>2.310925677898703</v>
       </c>
       <c r="F7" t="n">
-        <v>13.31060154401913</v>
+        <v>2.162972750903108</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.511239258575722</v>
+        <v>0.7330763795185548</v>
       </c>
       <c r="D8" t="n">
-        <v>2.544258573536645</v>
+        <v>0.4134420181997048</v>
       </c>
       <c r="E8" t="n">
-        <v>14.22108109476125</v>
+        <v>2.310925677898703</v>
       </c>
       <c r="F8" t="n">
-        <v>13.31060154401913</v>
+        <v>2.162972750903108</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
